--- a/artfynd/A 34569-2026 artfynd.xlsx
+++ b/artfynd/A 34569-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136935061</v>
       </c>
       <c r="B2" t="n">
-        <v>83448</v>
+        <v>83452</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34569-2026 artfynd.xlsx
+++ b/artfynd/A 34569-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136935061</v>
       </c>
       <c r="B2" t="n">
-        <v>83452</v>
+        <v>83454</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34569-2026 artfynd.xlsx
+++ b/artfynd/A 34569-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136935061</v>
       </c>
       <c r="B2" t="n">
-        <v>83454</v>
+        <v>83455</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34569-2026 artfynd.xlsx
+++ b/artfynd/A 34569-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136935061</v>
       </c>
       <c r="B2" t="n">
-        <v>83455</v>
+        <v>83459</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34569-2026 artfynd.xlsx
+++ b/artfynd/A 34569-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136935061</v>
       </c>
       <c r="B2" t="n">
-        <v>83459</v>
+        <v>83461</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34569-2026 artfynd.xlsx
+++ b/artfynd/A 34569-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136935061</v>
       </c>
       <c r="B2" t="n">
-        <v>83461</v>
+        <v>83474</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1206,7 +1206,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Cecilia Persson, Tomas Fasth</t>
+          <t>Tomas Fasth, Cecilia Persson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 34569-2026 artfynd.xlsx
+++ b/artfynd/A 34569-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136935061</v>
       </c>
       <c r="B2" t="n">
-        <v>83474</v>
+        <v>83476</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1206,7 +1206,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Tomas Fasth, Cecilia Persson</t>
+          <t>Cecilia Persson, Tomas Fasth</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 34569-2026 artfynd.xlsx
+++ b/artfynd/A 34569-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136935061</v>
       </c>
       <c r="B2" t="n">
-        <v>83476</v>
+        <v>83479</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34569-2026 artfynd.xlsx
+++ b/artfynd/A 34569-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136935061</v>
       </c>
       <c r="B2" t="n">
-        <v>83479</v>
+        <v>83489</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136930274</v>
       </c>
       <c r="B3" t="n">
-        <v>5182</v>
+        <v>5188</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>136930551</v>
       </c>
       <c r="B4" t="n">
-        <v>5182</v>
+        <v>5188</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1005,7 +1005,7 @@
         <v>136930356</v>
       </c>
       <c r="B5" t="n">
-        <v>5202</v>
+        <v>5208</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>136930420</v>
       </c>
       <c r="B6" t="n">
-        <v>5202</v>
+        <v>5208</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 34569-2026 artfynd.xlsx
+++ b/artfynd/A 34569-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136935061</v>
       </c>
       <c r="B2" t="n">
-        <v>83489</v>
+        <v>83492</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34569-2026 artfynd.xlsx
+++ b/artfynd/A 34569-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136935061</v>
       </c>
       <c r="B2" t="n">
-        <v>83492</v>
+        <v>83497</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34569-2026 artfynd.xlsx
+++ b/artfynd/A 34569-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136935061</v>
       </c>
       <c r="B2" t="n">
-        <v>83497</v>
+        <v>83508</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34569-2026 artfynd.xlsx
+++ b/artfynd/A 34569-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136935061</v>
       </c>
       <c r="B2" t="n">
-        <v>83508</v>
+        <v>83509</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1206,7 +1206,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Cecilia Persson, Tomas Fasth</t>
+          <t>Tomas Fasth, Cecilia Persson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 34569-2026 artfynd.xlsx
+++ b/artfynd/A 34569-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136935061</v>
       </c>
       <c r="B2" t="n">
-        <v>83509</v>
+        <v>83511</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1206,7 +1206,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Tomas Fasth, Cecilia Persson</t>
+          <t>Cecilia Persson, Tomas Fasth</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 34569-2026 artfynd.xlsx
+++ b/artfynd/A 34569-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136935061</v>
       </c>
       <c r="B2" t="n">
-        <v>83511</v>
+        <v>83512</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34569-2026 artfynd.xlsx
+++ b/artfynd/A 34569-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136935061</v>
       </c>
       <c r="B2" t="n">
-        <v>83512</v>
+        <v>83515</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
